--- a/ig/ekg/StructureDefinition-medcom-ekg-recording-composition.xlsx
+++ b/ig/ekg/StructureDefinition-medcom-ekg-recording-composition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.2</t>
+    <t>2.0.0-trial-use-2026-04-28</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:08:45+00:00</t>
+    <t>2026-04-29T09:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-medcom-canonical-semver:The canonical SHALL include an explicit semantic version (semver) with optional prerelease (-...) and build metadata (+...). {matches('^.*[|][0-9]+[.][0-9]+([.][0-9]+)?(-[0-9A-Za-z-]+([.][0-9A-Za-z-]+)*)?([+][0-9A-Za-z-]+([.][0-9A-Za-z-]+)*)?$')}medcom-canonical-fixed-major:If a version is present in the canonical, MAJOR SHALL be a fixed value. {matches('^.*[|]1[.].*$')}</t>
+medcom-canonical-semver:The canonical SHALL include an explicit semantic version (semver) with optional prerelease (-...) and build metadata (+...). {matches('^.*[|][0-9]+[.][0-9]+([.][0-9]+)?(-[0-9A-Za-z-]+([.][0-9A-Za-z-]+)*)?([+][0-9A-Za-z-]+([.][0-9A-Za-z-]+)*)?$')}medcom-canonical-fixed-major:If a version is present in the canonical, MAJOR SHALL be a fixed value. {matches('^.*[|]2[.].*$')}</t>
   </si>
   <si>
     <t>Composition.meta.security</t>

--- a/ig/ekg/StructureDefinition-medcom-ekg-recording-composition.xlsx
+++ b/ig/ekg/StructureDefinition-medcom-ekg-recording-composition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-trial-use-2026-04-28</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:39:42+00:00</t>
+    <t>2026-06-04T11:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1661,7 +1661,7 @@
     <t>Composition.event.period.start</t>
   </si>
   <si>
-    <t>The end time of the EKG recording</t>
+    <t>The start time of the EKG recording</t>
   </si>
   <si>
     <t>The start of the period. The boundary is inclusive.</t>
@@ -1687,7 +1687,7 @@
     <t>Composition.event.period.end</t>
   </si>
   <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
+    <t>The end time of the EKG recording</t>
   </si>
   <si>
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
